--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_supbrut_a_2018_aysen.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_supbrut_a_2018_aysen.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:46</t>
+    <t xml:space="preserve">2026-09-24 00:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -672,10 +672,10 @@
         <v>-0.38</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.31</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="9">
@@ -692,13 +692,13 @@
         <v>10</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="10">
@@ -718,7 +718,7 @@
         <v>-0.21</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>-0.45</v>
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.58</v>
+        <v>-0.59</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>-0.57</v>
